--- a/diseases/d133/2026-2029.xlsx
+++ b/diseases/d133/2026-2029.xlsx
@@ -14695,12 +14695,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -14734,81 +14734,95 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>101</v>
+        <v>54</v>
       </c>
       <c r="O76" t="n">
-        <v>101</v>
+        <v>54</v>
       </c>
       <c r="R76" t="n">
-        <v>0.02893688514097079</v>
+        <v>0.5046235431273006</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ESBL_CARBA</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS76" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ESBL_CARBA</t>
+        </is>
+      </c>
       <c r="AT76" t="n">
         <v>1</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14854,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -14879,41 +14893,44 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>101</v>
+        <v>54</v>
+      </c>
+      <c r="O77" t="n">
+        <v>54</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>SER_US_CPO_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_ESBL_CARBA</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>SER_US_CPO_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_ESBL_CARBA</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Carbapenemase-Producing Organisms (CPO), Total</t>
+          <t>ESBL-CARBA</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>organism_detections</t>
+          <t>case_notifications</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
@@ -14923,7 +14940,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD77" t="inlineStr">
@@ -14933,17 +14950,17 @@
       </c>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>narrower</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>not_comparable</t>
         </is>
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>reported_aggregate</t>
+          <t>non_additive</t>
         </is>
       </c>
       <c r="AH77" t="inlineStr">
@@ -14958,84 +14975,88 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>US_NNDSS_CPO_current</t>
+          <t>SE_FOHM_SMINET_ESBL_CARBA</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>United States NNDSS broad CPO reports; the source label does not establish infection rather than colonization.</t>
+          <t>Swedish ESBL-CARBA surveillance is a carbapenemase-mechanism category and is not interchangeable with phenotypic CRE surveillance.</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS77" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ESBL_CARBA</t>
+        </is>
+      </c>
       <c r="AT77" t="n">
         <v>1</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -15097,7 +15118,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -15106,13 +15127,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="O78" t="n">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="R78" t="n">
-        <v>0.01375218303729305</v>
+        <v>0.02893688514097079</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -15242,7 +15263,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -15251,7 +15272,7 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
@@ -15469,7 +15490,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -15478,13 +15499,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="O80" t="n">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="R80" t="n">
-        <v>0.02177428980904733</v>
+        <v>0.01375218303729305</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -15614,7 +15635,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -15623,7 +15644,7 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
@@ -15841,7 +15862,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -15850,13 +15871,13 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="O82" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="R82" t="n">
-        <v>0.01719022879661631</v>
+        <v>0.02177428980904733</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -15986,7 +16007,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -15995,7 +16016,7 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="U83" t="inlineStr">
         <is>
@@ -16213,7 +16234,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -16222,13 +16243,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="O84" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="R84" t="n">
-        <v>0.0237798165019859</v>
+        <v>0.01719022879661631</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -16358,7 +16379,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -16367,7 +16388,7 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="U85" t="inlineStr">
         <is>
@@ -16522,6 +16543,378 @@
         </is>
       </c>
       <c r="BC85" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>carbapenemase-producing-organisms-surveillance</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>产碳青霉烯酶微生物监测</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>83</v>
+      </c>
+      <c r="O86" t="n">
+        <v>83</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0.0237798165019859</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP86" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr"/>
+      <c r="AT86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV86" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA86" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB86" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC86" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>carbapenemase-producing-organisms-surveillance</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>产碳青霉烯酶微生物监测</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>83</v>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>SER_US_CPO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>SER_US_CPO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Carbapenemase-Producing Organisms (CPO), Total</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>organism_detections</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>US_NNDSS_CPO_current</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>United States NNDSS broad CPO reports; the source label does not establish infection rather than colonization.</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP87" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr"/>
+      <c r="AT87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV87" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA87" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB87" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC87" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -16643,7 +17036,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
@@ -16653,7 +17046,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11">
@@ -16673,7 +17066,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">
@@ -16705,7 +17098,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2311</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d133/2026-2029.xlsx
+++ b/diseases/d133/2026-2029.xlsx
@@ -16920,6 +16920,378 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>carbapenemase-producing-organisms-surveillance</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>产碳青霉烯酶微生物监测</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>52</v>
+      </c>
+      <c r="O88" t="n">
+        <v>52</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0.0148981982904008</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP88" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr"/>
+      <c r="AT88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV88" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA88" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB88" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC88" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>carbapenemase-producing-organisms-surveillance</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>产碳青霉烯酶微生物监测</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>52</v>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>SER_US_CPO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>SER_US_CPO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Carbapenemase-Producing Organisms (CPO), Total</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>organism_detections</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>US_NNDSS_CPO_current</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>United States NNDSS broad CPO reports; the source label does not establish infection rather than colonization.</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP89" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr"/>
+      <c r="AT89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV89" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA89" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB89" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC89" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16953,7 +17325,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -17036,7 +17408,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -17046,7 +17418,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11">
@@ -17066,7 +17438,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">
@@ -17098,7 +17470,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2365</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d133/2026-2029.xlsx
+++ b/diseases/d133/2026-2029.xlsx
@@ -17292,6 +17292,378 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>carbapenemase-producing-organisms-surveillance</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>产碳青霉烯酶微生物监测</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>65</v>
+      </c>
+      <c r="O90" t="n">
+        <v>65</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0.018622747863001</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP90" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr"/>
+      <c r="AT90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV90" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA90" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB90" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC90" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>carbapenemase-producing-organisms-surveillance</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>产碳青霉烯酶微生物监测</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>65</v>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>SER_US_CPO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>SER_US_CPO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Carbapenemase-Producing Organisms (CPO), Total</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>organism_detections</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD91" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>US_NNDSS_CPO_current</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>United States NNDSS broad CPO reports; the source label does not establish infection rather than colonization.</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP91" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr"/>
+      <c r="AT91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV91" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA91" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB91" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC91" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17325,7 +17697,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -17408,7 +17780,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
@@ -17418,7 +17790,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -17438,7 +17810,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13">
@@ -17470,7 +17842,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2417</v>
+        <v>2482</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d133/2026-2029.xlsx
+++ b/diseases/d133/2026-2029.xlsx
@@ -17664,6 +17664,378 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>carbapenemase-producing-organisms-surveillance</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>产碳青霉烯酶微生物监测</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>51</v>
+      </c>
+      <c r="O92" t="n">
+        <v>51</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0.01461169447712387</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP92" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr"/>
+      <c r="AT92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV92" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA92" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB92" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC92" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>carbapenemase-producing-organisms-surveillance</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>产碳青霉烯酶微生物监测</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>51</v>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>SER_US_CPO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>SER_US_CPO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Carbapenemase-Producing Organisms (CPO), Total</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>organism_detections</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD93" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>US_NNDSS_CPO_current</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>United States NNDSS broad CPO reports; the source label does not establish infection rather than colonization.</t>
+        </is>
+      </c>
+      <c r="AM93" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP93" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr"/>
+      <c r="AT93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV93" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA93" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB93" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC93" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17697,7 +18069,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -17780,7 +18152,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
@@ -17790,7 +18162,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11">
@@ -17810,7 +18182,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13">
@@ -17842,7 +18214,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2482</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d133/2026-2029.xlsx
+++ b/diseases/d133/2026-2029.xlsx
@@ -18036,6 +18036,378 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>carbapenemase-producing-organisms-surveillance</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>产碳青霉烯酶微生物监测</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>66</v>
+      </c>
+      <c r="O94" t="n">
+        <v>66</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0.01890925167627794</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP94" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr"/>
+      <c r="AT94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV94" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA94" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB94" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC94" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>carbapenemase-producing-organisms-surveillance</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>产碳青霉烯酶微生物监测</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>66</v>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>SER_US_CPO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>SER_US_CPO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Carbapenemase-Producing Organisms (CPO), Total</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>organism_detections</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>US_NNDSS_CPO_current</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>United States NNDSS broad CPO reports; the source label does not establish infection rather than colonization.</t>
+        </is>
+      </c>
+      <c r="AM95" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr"/>
+      <c r="AT95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV95" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA95" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB95" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC95" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18069,7 +18441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -18152,7 +18524,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10">
@@ -18162,7 +18534,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11">
@@ -18182,7 +18554,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
@@ -18214,7 +18586,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2533</v>
+        <v>2599</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d133/2026-2029.xlsx
+++ b/diseases/d133/2026-2029.xlsx
@@ -1169,6 +1169,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1544,6 +1549,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1919,6 +1929,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2294,6 +2309,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2669,6 +2689,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3437,6 +3462,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3812,6 +3842,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4187,6 +4222,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4562,6 +4602,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5330,6 +5375,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5705,6 +5755,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6080,6 +6135,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6455,6 +6515,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7223,6 +7288,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7598,6 +7668,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7973,6 +8048,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8348,6 +8428,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9116,6 +9201,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9491,6 +9581,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9866,6 +9961,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10241,6 +10341,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10613,6 +10718,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11378,6 +11488,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11750,6 +11865,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12122,6 +12242,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12494,6 +12619,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13259,6 +13389,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13631,6 +13766,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14003,6 +14143,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14375,6 +14520,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15140,6 +15290,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15512,6 +15667,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15884,6 +16044,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16256,6 +16421,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16628,6 +16798,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16948,12 +17123,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -16978,7 +17153,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -16987,81 +17162,95 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="O88" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="R88" t="n">
-        <v>0.0148981982904008</v>
+        <v>0.6541416299798342</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ESBL_CARBA</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS88" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ESBL_CARBA</t>
+        </is>
+      </c>
       <c r="AT88" t="n">
         <v>1</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -17093,12 +17282,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -17123,7 +17312,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -17132,41 +17321,44 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>52</v>
+        <v>70</v>
+      </c>
+      <c r="O89" t="n">
+        <v>70</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>SER_US_CPO_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_ESBL_CARBA</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>SER_US_CPO_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_ESBL_CARBA</t>
         </is>
       </c>
       <c r="W89" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Carbapenemase-Producing Organisms (CPO), Total</t>
+          <t>ESBL-CARBA</t>
         </is>
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>organism_detections</t>
+          <t>case_notifications</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
@@ -17176,7 +17368,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD89" t="inlineStr">
@@ -17186,17 +17378,17 @@
       </c>
       <c r="AE89" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>narrower</t>
         </is>
       </c>
       <c r="AF89" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>not_comparable</t>
         </is>
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>reported_aggregate</t>
+          <t>non_additive</t>
         </is>
       </c>
       <c r="AH89" t="inlineStr">
@@ -17211,84 +17403,88 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>US_NNDSS_CPO_current</t>
+          <t>SE_FOHM_SMINET_ESBL_CARBA</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>United States NNDSS broad CPO reports; the source label does not establish infection rather than colonization.</t>
+          <t>Swedish ESBL-CARBA surveillance is a carbapenemase-mechanism category and is not interchangeable with phenotypic CRE surveillance.</t>
         </is>
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS89" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ89" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_ESBL_CARBA</t>
+        </is>
+      </c>
       <c r="AT89" t="n">
         <v>1</v>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -17350,7 +17546,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -17359,17 +17555,22 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="O90" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="R90" t="n">
-        <v>0.018622747863001</v>
+        <v>0.0148981982904008</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -17495,7 +17696,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -17504,7 +17705,7 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
@@ -17722,7 +17923,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -17731,17 +17932,22 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="O92" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="R92" t="n">
-        <v>0.01461169447712387</v>
+        <v>0.018622747863001</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -17867,7 +18073,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -17876,7 +18082,7 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
@@ -18094,7 +18300,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -18103,17 +18309,22 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="O94" t="n">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="R94" t="n">
-        <v>0.01890925167627794</v>
+        <v>0.01461169447712387</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -18239,7 +18450,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -18248,7 +18459,7 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="U95" t="inlineStr">
         <is>
@@ -18403,6 +18614,760 @@
         </is>
       </c>
       <c r="BC95" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>carbapenemase-producing-organisms-surveillance</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>产碳青霉烯酶微生物监测</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>66</v>
+      </c>
+      <c r="O96" t="n">
+        <v>66</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0.01890925167627794</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP96" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr"/>
+      <c r="AT96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV96" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA96" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB96" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC96" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>carbapenemase-producing-organisms-surveillance</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>产碳青霉烯酶微生物监测</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>66</v>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>SER_US_CPO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>SER_US_CPO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Carbapenemase-Producing Organisms (CPO), Total</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>organism_detections</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>US_NNDSS_CPO_current</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>United States NNDSS broad CPO reports; the source label does not establish infection rather than colonization.</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP97" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr"/>
+      <c r="AT97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV97" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA97" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB97" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC97" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>carbapenemase-producing-organisms-surveillance</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>产碳青霉烯酶微生物监测</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>76</v>
+      </c>
+      <c r="O98" t="n">
+        <v>76</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0.02177428980904733</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP98" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr"/>
+      <c r="AT98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV98" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA98" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB98" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC98" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>carbapenemase-producing-organisms-surveillance</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>产碳青霉烯酶微生物监测</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>76</v>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>SER_US_CPO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>SER_US_CPO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Carbapenemase-Producing Organisms (CPO), Total</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>organism_detections</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>US_NNDSS_CPO_current</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>United States NNDSS broad CPO reports; the source label does not establish infection rather than colonization.</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP99" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr"/>
+      <c r="AT99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV99" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA99" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB99" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC99" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -18441,7 +19406,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -18524,7 +19489,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
@@ -18534,7 +19499,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11">
@@ -18554,7 +19519,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
@@ -18586,7 +19551,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2599</v>
+        <v>2745</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d133/2026-2029.xlsx
+++ b/diseases/d133/2026-2029.xlsx
@@ -17162,13 +17162,13 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O88" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R88" t="n">
-        <v>0.6541416299798342</v>
+        <v>0.6447967495515509</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -17321,10 +17321,10 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O89" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2745</v>
+        <v>2744</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d133/2026-2029.xlsx
+++ b/diseases/d133/2026-2029.xlsx
@@ -1158,9 +1158,6 @@
       <c r="O4" t="n">
         <v>2</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -1538,9 +1535,6 @@
       <c r="O6" t="n">
         <v>106</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.03036940420735549</v>
       </c>
@@ -1918,9 +1912,6 @@
       <c r="O8" t="n">
         <v>106</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.03036940420735549</v>
       </c>
@@ -2298,9 +2289,6 @@
       <c r="O10" t="n">
         <v>100</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.02865038132769385</v>
       </c>
@@ -2678,9 +2666,6 @@
       <c r="O12" t="n">
         <v>47</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.01346567922401611</v>
       </c>
@@ -3451,9 +3436,6 @@
       <c r="O16" t="n">
         <v>97</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.02779086988786304</v>
       </c>
@@ -3831,9 +3813,6 @@
       <c r="O18" t="n">
         <v>33</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.009454625838138971</v>
       </c>
@@ -4211,9 +4190,6 @@
       <c r="O20" t="n">
         <v>71</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.02034177074266263</v>
       </c>
@@ -4591,9 +4567,6 @@
       <c r="O22" t="n">
         <v>61</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.01747673260989325</v>
       </c>
@@ -5364,9 +5337,6 @@
       <c r="O26" t="n">
         <v>48</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.01375218303729305</v>
       </c>
@@ -5744,9 +5714,6 @@
       <c r="O28" t="n">
         <v>29</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.008308610585031217</v>
       </c>
@@ -6124,9 +6091,6 @@
       <c r="O30" t="n">
         <v>86</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.02463932794181671</v>
       </c>
@@ -6504,9 +6468,6 @@
       <c r="O32" t="n">
         <v>43</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.01231966397090836</v>
       </c>
@@ -7277,9 +7238,6 @@
       <c r="O36" t="n">
         <v>45</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.01289267159746223</v>
       </c>
@@ -7657,9 +7615,6 @@
       <c r="O38" t="n">
         <v>54</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.01547120591695468</v>
       </c>
@@ -8037,9 +7992,6 @@
       <c r="O40" t="n">
         <v>28</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.00802210677175428</v>
       </c>
@@ -8417,9 +8369,6 @@
       <c r="O42" t="n">
         <v>59</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.01690372498333937</v>
       </c>
@@ -9190,9 +9139,6 @@
       <c r="O46" t="n">
         <v>68</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.01948225930283182</v>
       </c>
@@ -9570,9 +9516,6 @@
       <c r="O48" t="n">
         <v>51</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.01461169447712387</v>
       </c>
@@ -9950,9 +9893,6 @@
       <c r="O50" t="n">
         <v>57</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.0163307173567855</v>
       </c>
@@ -10330,9 +10270,6 @@
       <c r="O52" t="n">
         <v>3</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -19368,6 +19305,383 @@
         </is>
       </c>
       <c r="BC99" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>carbapenemase-producing-organisms-surveillance</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>产碳青霉烯酶微生物监测</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>50</v>
+      </c>
+      <c r="O100" t="n">
+        <v>50</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0.01432519066384693</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP100" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr"/>
+      <c r="AT100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV100" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA100" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB100" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC100" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>carbapenemase-producing-organisms-surveillance</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>D133</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Carbapenemase-producing organisms surveillance</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>产碳青霉烯酶微生物监测</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>50</v>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>SER_US_CPO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>SER_US_CPO_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Carbapenemase-Producing Organisms (CPO), Total</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>organism_detections</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>reported_aggregate</t>
+        </is>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>US_NNDSS_CPO_current</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>United States NNDSS broad CPO reports; the source label does not establish infection rather than colonization.</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP101" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr"/>
+      <c r="AT101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV101" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA101" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB101" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC101" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -19406,7 +19720,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -19489,7 +19803,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
@@ -19499,7 +19813,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -19519,7 +19833,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
@@ -19551,7 +19865,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2744</v>
+        <v>2794</v>
       </c>
     </row>
     <row r="16">
